--- a/public/exports-from-60-with-coowners/29189757.xlsx
+++ b/public/exports-from-60-with-coowners/29189757.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -10039,7 +10039,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">200054922</t>
+          <t xml:space="preserve">200054923</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -16639,7 +16639,7 @@
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257717</t>
+          <t xml:space="preserve">311257874</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -16714,7 +16714,7 @@
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257717</t>
+          <t xml:space="preserve">311257874</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
@@ -16864,7 +16864,7 @@
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257717</t>
+          <t xml:space="preserve">311257874</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -16939,7 +16939,7 @@
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257717</t>
+          <t xml:space="preserve">311257874</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -17014,7 +17014,7 @@
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257717</t>
+          <t xml:space="preserve">311257874</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">

--- a/public/exports-from-60-with-coowners/29189757.xlsx
+++ b/public/exports-from-60-with-coowners/29189757.xlsx
@@ -10039,7 +10039,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">200054923</t>
+          <t xml:space="preserve">200054922</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -16264,7 +16264,7 @@
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255967</t>
+          <t xml:space="preserve">311255968</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -16339,7 +16339,7 @@
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255967</t>
+          <t xml:space="preserve">311255968</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">

--- a/public/exports-from-60-with-coowners/29189757.xlsx
+++ b/public/exports-from-60-with-coowners/29189757.xlsx
@@ -16264,7 +16264,7 @@
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255968</t>
+          <t xml:space="preserve">311255967</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -16339,7 +16339,7 @@
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255968</t>
+          <t xml:space="preserve">311255967</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -16639,7 +16639,7 @@
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257874</t>
+          <t xml:space="preserve">311257717</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -16714,7 +16714,7 @@
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257874</t>
+          <t xml:space="preserve">311257717</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
@@ -16864,7 +16864,7 @@
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257874</t>
+          <t xml:space="preserve">311257717</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -16939,7 +16939,7 @@
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257874</t>
+          <t xml:space="preserve">311257717</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -17014,7 +17014,7 @@
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257874</t>
+          <t xml:space="preserve">311257717</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
